--- a/data/beer_dataset.xlsx
+++ b/data/beer_dataset.xlsx
@@ -13,16 +13,13 @@
   </bookViews>
   <sheets>
     <sheet name="dataset" sheetId="1" r:id="rId1"/>
-    <sheet name="diccionario" sheetId="2" r:id="rId2"/>
-    <sheet name="resumen_estadistico" sheetId="3" r:id="rId3"/>
-    <sheet name="leyenda_colores" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="347">
   <si>
     <t>year_month</t>
   </si>
@@ -66,9 +63,6 @@
     <t>employment_thousands</t>
   </si>
   <si>
-    <t>temp_feb_f</t>
-  </si>
-  <si>
     <t>2012-01</t>
   </si>
   <si>
@@ -1063,276 +1057,6 @@
   </si>
   <si>
     <t>2025-10-01</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Categoría</t>
-  </si>
-  <si>
-    <t>Unidad</t>
-  </si>
-  <si>
-    <t>Fuente</t>
-  </si>
-  <si>
-    <t>Descripción</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>YYYY-MM</t>
-  </si>
-  <si>
-    <t>TTB / FRED</t>
-  </si>
-  <si>
-    <t>Identificador temporal del mes</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>Fecha completa del primer día del mes</t>
-  </si>
-  <si>
-    <t>Target (variable a predecir)</t>
-  </si>
-  <si>
-    <t>Barriles (31 gal = 1 bbl)</t>
-  </si>
-  <si>
-    <t>TTB Beer Report</t>
-  </si>
-  <si>
-    <t>Producción total mensual de cerveza en USA</t>
-  </si>
-  <si>
-    <t>Variable TTB</t>
-  </si>
-  <si>
-    <t>Barriles</t>
-  </si>
-  <si>
-    <t>Inventario en stock al fin de cada mes</t>
-  </si>
-  <si>
-    <t>Cerveza retirada con impuesto pagado (proxy ventas domésticas)</t>
-  </si>
-  <si>
-    <t>Cerveza exportada libre de impuesto</t>
-  </si>
-  <si>
-    <t>Insumo producción</t>
-  </si>
-  <si>
-    <t>Índice (base 1982=100)</t>
-  </si>
-  <si>
-    <t>FRED WPU012201</t>
-  </si>
-  <si>
-    <t>Precio productor de cebada en USA</t>
-  </si>
-  <si>
-    <t>USD por tonelada métrica</t>
-  </si>
-  <si>
-    <t>FRED PBARLUSDM</t>
-  </si>
-  <si>
-    <t>Precio global de cebada (FMI). 5 faltantes al inicio.</t>
-  </si>
-  <si>
-    <t>Costos sector</t>
-  </si>
-  <si>
-    <t>Índice (base 2003=100)</t>
-  </si>
-  <si>
-    <t>FRED PCU3121231212</t>
-  </si>
-  <si>
-    <t>PPI de cervecerías — costos de producción del sector</t>
-  </si>
-  <si>
-    <t>Índice (base 1992=100)</t>
-  </si>
-  <si>
-    <t>FRED PCU3121203121207</t>
-  </si>
-  <si>
-    <t>PPI de cerveza en barril — precios al productor</t>
-  </si>
-  <si>
-    <t>Actividad sectorial</t>
-  </si>
-  <si>
-    <t>Índice (base 2017=100)</t>
-  </si>
-  <si>
-    <t>FRED IPG3121S</t>
-  </si>
-  <si>
-    <t>Producción industrial de bebidas en general</t>
-  </si>
-  <si>
-    <t>Demanda</t>
-  </si>
-  <si>
-    <t>Miles de mill. USD (real)</t>
-  </si>
-  <si>
-    <t>FRED DSPIC96</t>
-  </si>
-  <si>
-    <t>Ingreso personal disponible real — poder adquisitivo</t>
-  </si>
-  <si>
-    <t>Índice</t>
-  </si>
-  <si>
-    <t>FRED USACSCICP02STSAM</t>
-  </si>
-  <si>
-    <t>Confianza del consumidor USA</t>
-  </si>
-  <si>
-    <t>Ciclo económico</t>
-  </si>
-  <si>
-    <t>Miles de empleos</t>
-  </si>
-  <si>
-    <t>FRED PAYEMS</t>
-  </si>
-  <si>
-    <t>Empleo total en nóminas no agrícolas</t>
-  </si>
-  <si>
-    <t>Clima</t>
-  </si>
-  <si>
-    <t>Grados Fahrenheit</t>
-  </si>
-  <si>
-    <t>NOAA NCEI</t>
-  </si>
-  <si>
-    <t>Temperatura promedio de febrero (zona continental USA). Proxy anual de invierno.</t>
-  </si>
-  <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>mean</t>
-  </si>
-  <si>
-    <t>std</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>max</t>
-  </si>
-  <si>
-    <t>faltantes</t>
-  </si>
-  <si>
-    <t>faltantes_%</t>
-  </si>
-  <si>
-    <t>LEYENDA — Colores del Dataset</t>
-  </si>
-  <si>
-    <t>🎯 Amarillo — TARGET</t>
-  </si>
-  <si>
-    <t>produced_barrels: variable a predecir en los modelos ML</t>
-  </si>
-  <si>
-    <t>📦 Azul — Variables TTB</t>
-  </si>
-  <si>
-    <t>Stocks, removals: datos internos del sector cervecero</t>
-  </si>
-  <si>
-    <t>📊 Verde — Variables FRED</t>
-  </si>
-  <si>
-    <t>Precios, PPI, IP, ingreso, confianza, empleo</t>
-  </si>
-  <si>
-    <t>🌡️ Naranja — Clima</t>
-  </si>
-  <si>
-    <t>Temperatura promedio febrero USA (variable anual)</t>
-  </si>
-  <si>
-    <t>NOTA SOBRE LA SERIE</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>2012-01 → 2025-10 (166 observaciones mensuales)</t>
-  </si>
-  <si>
-    <t>Fuente principal</t>
-  </si>
-  <si>
-    <t>TTB Beer Report (Alcohol &amp; Tobacco Tax &amp; Trade Bureau)</t>
-  </si>
-  <si>
-    <t>Variables externas</t>
-  </si>
-  <si>
-    <t>FRED (Federal Reserve Bank of St. Louis)</t>
-  </si>
-  <si>
-    <t>NOAA NCEI — temperatura promedio febrero zona continental USA</t>
-  </si>
-  <si>
-    <t>Datos faltantes</t>
-  </si>
-  <si>
-    <t>price_barley_global: 5 faltantes al inicio (2012-01 a 2012-05)</t>
-  </si>
-  <si>
-    <t>CÓMO USAR EN COLAB</t>
-  </si>
-  <si>
-    <t>Paso 1</t>
-  </si>
-  <si>
-    <t>Subir el archivo beer_dataset.xlsx a tu Google Drive</t>
-  </si>
-  <si>
-    <t>Paso 2</t>
-  </si>
-  <si>
-    <t>from google.colab import drive; drive.mount('/content/drive')</t>
-  </si>
-  <si>
-    <t>Paso 3</t>
-  </si>
-  <si>
-    <t>df = pd.read_excel('/content/drive/MyDrive/beer_dataset.xlsx', sheet_name='dataset')</t>
   </si>
   <si>
     <t>temp_prom</t>
@@ -1342,7 +1066,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1363,15 +1087,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1408,16 +1125,6 @@
         <fgColor rgb="FFF9F9F9"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1446,7 +1153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1489,57 +1196,6 @@
     </xf>
     <xf numFmtId="4" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1903,15 +1559,15 @@
         <v>13</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>437</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>16</v>
       </c>
       <c r="C2" s="7">
         <v>15213274</v>
@@ -1953,10 +1609,10 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>18</v>
       </c>
       <c r="C3" s="13">
         <v>15078300</v>
@@ -1998,10 +1654,10 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>20</v>
       </c>
       <c r="C4" s="7">
         <v>17278351</v>
@@ -2043,10 +1699,10 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>22</v>
       </c>
       <c r="C5" s="13">
         <v>16709639</v>
@@ -2088,10 +1744,10 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C6" s="7">
         <v>18077414</v>
@@ -2133,10 +1789,10 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>26</v>
       </c>
       <c r="C7" s="13">
         <v>18450246</v>
@@ -2180,10 +1836,10 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="C8" s="7">
         <v>17966874</v>
@@ -2227,10 +1883,10 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>30</v>
       </c>
       <c r="C9" s="13">
         <v>17338445</v>
@@ -2274,10 +1930,10 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C10" s="7">
         <v>15951915</v>
@@ -2321,10 +1977,10 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>34</v>
       </c>
       <c r="C11" s="13">
         <v>15217587</v>
@@ -2368,10 +2024,10 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="C12" s="7">
         <v>14484586</v>
@@ -2415,10 +2071,10 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>38</v>
       </c>
       <c r="C13" s="13">
         <v>14407647</v>
@@ -2462,10 +2118,10 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C14" s="7">
         <v>15049142</v>
@@ -2509,10 +2165,10 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>42</v>
       </c>
       <c r="C15" s="13">
         <v>14612869</v>
@@ -2556,10 +2212,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="C16" s="7">
         <v>16326143</v>
@@ -2603,10 +2259,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>46</v>
       </c>
       <c r="C17" s="13">
         <v>16280979</v>
@@ -2650,10 +2306,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C18" s="7">
         <v>17563301</v>
@@ -2697,10 +2353,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>50</v>
       </c>
       <c r="C19" s="13">
         <v>17930892</v>
@@ -2744,10 +2400,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C20" s="7">
         <v>17364239</v>
@@ -2791,10 +2447,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>54</v>
       </c>
       <c r="C21" s="13">
         <v>17253631</v>
@@ -2838,10 +2494,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="C22" s="7">
         <v>16045575</v>
@@ -2885,10 +2541,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>57</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>58</v>
       </c>
       <c r="C23" s="13">
         <v>15521566</v>
@@ -2932,10 +2588,10 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="C24" s="7">
         <v>13948891</v>
@@ -2979,10 +2635,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>61</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>62</v>
       </c>
       <c r="C25" s="13">
         <v>14233164</v>
@@ -3026,10 +2682,10 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="C26" s="7">
         <v>15382498</v>
@@ -3073,10 +2729,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="C27" s="13">
         <v>14458404</v>
@@ -3120,10 +2776,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="C28" s="7">
         <v>16360344</v>
@@ -3167,10 +2823,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="C29" s="13">
         <v>16486367</v>
@@ -3214,10 +2870,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="C30" s="7">
         <v>17710016</v>
@@ -3261,10 +2917,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="C31" s="13">
         <v>18205630</v>
@@ -3308,10 +2964,10 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="C32" s="7">
         <v>17675101</v>
@@ -3355,10 +3011,10 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="C33" s="13">
         <v>16370370</v>
@@ -3402,10 +3058,10 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="C34" s="7">
         <v>16663864</v>
@@ -3449,10 +3105,10 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>82</v>
       </c>
       <c r="C35" s="13">
         <v>15492902</v>
@@ -3496,10 +3152,10 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C36" s="7">
         <v>13568782</v>
@@ -3543,10 +3199,10 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="12" t="s">
         <v>85</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>86</v>
       </c>
       <c r="C37" s="13">
         <v>14505242</v>
@@ -3590,10 +3246,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="C38" s="7">
         <v>14609862</v>
@@ -3637,10 +3293,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>89</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>90</v>
       </c>
       <c r="C39" s="13">
         <v>14359692</v>
@@ -3684,10 +3340,10 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>92</v>
       </c>
       <c r="C40" s="7">
         <v>16763815</v>
@@ -3731,10 +3387,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B41" s="12" t="s">
         <v>93</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>94</v>
       </c>
       <c r="C41" s="13">
         <v>16436773</v>
@@ -3778,10 +3434,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="C42" s="7">
         <v>17405509</v>
@@ -3825,10 +3481,10 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B43" s="12" t="s">
         <v>97</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>98</v>
       </c>
       <c r="C43" s="13">
         <v>18260094</v>
@@ -3872,10 +3528,10 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="C44" s="7">
         <v>17151177</v>
@@ -3919,10 +3575,10 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="C45" s="13">
         <v>16834688</v>
@@ -3966,10 +3622,10 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="C46" s="7">
         <v>16615866</v>
@@ -4013,10 +3669,10 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>106</v>
       </c>
       <c r="C47" s="13">
         <v>15469409</v>
@@ -4060,10 +3716,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="C48" s="7">
         <v>14014762</v>
@@ -4107,10 +3763,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>110</v>
       </c>
       <c r="C49" s="13">
         <v>14714889</v>
@@ -4154,10 +3810,10 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="C50" s="7">
         <v>14544184</v>
@@ -4201,10 +3857,10 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>114</v>
       </c>
       <c r="C51" s="13">
         <v>14493903</v>
@@ -4248,10 +3904,10 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="C52" s="7">
         <v>17229663</v>
@@ -4295,10 +3951,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="12" t="s">
         <v>117</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>118</v>
       </c>
       <c r="C53" s="13">
         <v>16504433</v>
@@ -4342,10 +3998,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="C54" s="7">
         <v>16990795</v>
@@ -4389,10 +4045,10 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>122</v>
       </c>
       <c r="C55" s="13">
         <v>18036154</v>
@@ -4436,10 +4092,10 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="C56" s="7">
         <v>16993344</v>
@@ -4483,10 +4139,10 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="C57" s="13">
         <v>17013486</v>
@@ -4530,10 +4186,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="C58" s="7">
         <v>15998877</v>
@@ -4577,10 +4233,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="C59" s="13">
         <v>14514652</v>
@@ -4624,10 +4280,10 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="C60" s="7">
         <v>13744364</v>
@@ -4671,10 +4327,10 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>134</v>
       </c>
       <c r="C61" s="13">
         <v>14592604</v>
@@ -4718,10 +4374,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="C62" s="7">
         <v>14559262</v>
@@ -4765,10 +4421,10 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>138</v>
       </c>
       <c r="C63" s="13">
         <v>13455629</v>
@@ -4812,10 +4468,10 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="C64" s="7">
         <v>16969822</v>
@@ -4859,10 +4515,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="12" t="s">
         <v>141</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>142</v>
       </c>
       <c r="C65" s="13">
         <v>15879025</v>
@@ -4906,10 +4562,10 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="C66" s="7">
         <v>17465472</v>
@@ -4953,10 +4609,10 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="12" t="s">
         <v>145</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>146</v>
       </c>
       <c r="C67" s="13">
         <v>18347273</v>
@@ -5000,10 +4656,10 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="C68" s="7">
         <v>16209451</v>
@@ -5047,10 +4703,10 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B69" s="12" t="s">
         <v>149</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>150</v>
       </c>
       <c r="C69" s="13">
         <v>16435044</v>
@@ -5094,10 +4750,10 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="C70" s="7">
         <v>15684180</v>
@@ -5141,10 +4797,10 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B71" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="B71" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="C71" s="13">
         <v>14807684</v>
@@ -5188,10 +4844,10 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="C72" s="7">
         <v>13529576</v>
@@ -5235,10 +4891,10 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" s="12" t="s">
         <v>157</v>
-      </c>
-      <c r="B73" s="12" t="s">
-        <v>158</v>
       </c>
       <c r="C73" s="13">
         <v>13236847</v>
@@ -5282,10 +4938,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>159</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>160</v>
       </c>
       <c r="C74" s="7">
         <v>13917107</v>
@@ -5329,10 +4985,10 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="B75" s="12" t="s">
         <v>161</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="C75" s="13">
         <v>13484580</v>
@@ -5376,10 +5032,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="C76" s="7">
         <v>16295808</v>
@@ -5423,10 +5079,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B77" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="C77" s="13">
         <v>15692038</v>
@@ -5470,10 +5126,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>168</v>
       </c>
       <c r="C78" s="7">
         <v>16846360</v>
@@ -5517,10 +5173,10 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="B79" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="B79" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="C79" s="13">
         <v>17999454</v>
@@ -5564,10 +5220,10 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="C80" s="7">
         <v>16584447</v>
@@ -5611,10 +5267,10 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="B81" s="12" t="s">
         <v>173</v>
-      </c>
-      <c r="B81" s="12" t="s">
-        <v>174</v>
       </c>
       <c r="C81" s="13">
         <v>16967085</v>
@@ -5658,10 +5314,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="C82" s="7">
         <v>15536290</v>
@@ -5705,10 +5361,10 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="12" t="s">
         <v>177</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>178</v>
       </c>
       <c r="C83" s="13">
         <v>14086455</v>
@@ -5752,10 +5408,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="C84" s="7">
         <v>12776166</v>
@@ -5799,10 +5455,10 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" s="12" t="s">
         <v>181</v>
-      </c>
-      <c r="B85" s="12" t="s">
-        <v>182</v>
       </c>
       <c r="C85" s="13">
         <v>13607499</v>
@@ -5846,10 +5502,10 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="C86" s="7">
         <v>13895825</v>
@@ -5893,10 +5549,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B87" s="12" t="s">
         <v>185</v>
-      </c>
-      <c r="B87" s="12" t="s">
-        <v>186</v>
       </c>
       <c r="C87" s="13">
         <v>13108594</v>
@@ -5940,10 +5596,10 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="C88" s="7">
         <v>16142261</v>
@@ -5987,10 +5643,10 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="B89" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="B89" s="12" t="s">
-        <v>190</v>
       </c>
       <c r="C89" s="13">
         <v>15578876</v>
@@ -6034,10 +5690,10 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="C90" s="7">
         <v>15976008</v>
@@ -6081,10 +5737,10 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="B91" s="12" t="s">
         <v>193</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>194</v>
       </c>
       <c r="C91" s="13">
         <v>17166333</v>
@@ -6128,10 +5784,10 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="C92" s="7">
         <v>15793261</v>
@@ -6175,10 +5831,10 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B93" s="12" t="s">
         <v>197</v>
-      </c>
-      <c r="B93" s="12" t="s">
-        <v>198</v>
       </c>
       <c r="C93" s="13">
         <v>15437866</v>
@@ -6222,10 +5878,10 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="C94" s="7">
         <v>15637821</v>
@@ -6269,10 +5925,10 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B95" s="12" t="s">
         <v>201</v>
-      </c>
-      <c r="B95" s="12" t="s">
-        <v>202</v>
       </c>
       <c r="C95" s="13">
         <v>14410419</v>
@@ -6316,10 +5972,10 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="C96" s="7">
         <v>12705535</v>
@@ -6363,10 +6019,10 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="B97" s="12" t="s">
         <v>205</v>
-      </c>
-      <c r="B97" s="12" t="s">
-        <v>206</v>
       </c>
       <c r="C97" s="13">
         <v>14569031</v>
@@ -6410,10 +6066,10 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>207</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="C98" s="7">
         <v>13896191</v>
@@ -6457,10 +6113,10 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B99" s="12" t="s">
         <v>209</v>
-      </c>
-      <c r="B99" s="12" t="s">
-        <v>210</v>
       </c>
       <c r="C99" s="13">
         <v>13026424</v>
@@ -6504,10 +6160,10 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>211</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>212</v>
       </c>
       <c r="C100" s="7">
         <v>15674106</v>
@@ -6551,10 +6207,10 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B101" s="12" t="s">
         <v>213</v>
-      </c>
-      <c r="B101" s="12" t="s">
-        <v>214</v>
       </c>
       <c r="C101" s="13">
         <v>13944164</v>
@@ -6598,10 +6254,10 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="C102" s="7">
         <v>14994553</v>
@@ -6645,10 +6301,10 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="B103" s="12" t="s">
         <v>217</v>
-      </c>
-      <c r="B103" s="12" t="s">
-        <v>218</v>
       </c>
       <c r="C103" s="13">
         <v>17444996</v>
@@ -6692,10 +6348,10 @@
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B104" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="C104" s="7">
         <v>16534810</v>
@@ -6739,10 +6395,10 @@
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A105" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="B105" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="B105" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="C105" s="13">
         <v>15825689</v>
@@ -6786,10 +6442,10 @@
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B106" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="C106" s="7">
         <v>16719142</v>
@@ -6833,10 +6489,10 @@
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="B107" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="B107" s="12" t="s">
-        <v>226</v>
       </c>
       <c r="C107" s="13">
         <v>14858754</v>
@@ -6880,10 +6536,10 @@
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B108" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="C108" s="7">
         <v>13415617</v>
@@ -6927,10 +6583,10 @@
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="B109" s="12" t="s">
         <v>229</v>
-      </c>
-      <c r="B109" s="12" t="s">
-        <v>230</v>
       </c>
       <c r="C109" s="13">
         <v>15507884</v>
@@ -6974,10 +6630,10 @@
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B110" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="C110" s="7">
         <v>14728459</v>
@@ -7021,10 +6677,10 @@
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B111" s="12" t="s">
         <v>233</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>234</v>
       </c>
       <c r="C111" s="13">
         <v>13303127</v>
@@ -7068,10 +6724,10 @@
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B112" s="6" t="s">
         <v>235</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>236</v>
       </c>
       <c r="C112" s="7">
         <v>15938790</v>
@@ -7115,10 +6771,10 @@
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B113" s="12" t="s">
         <v>237</v>
-      </c>
-      <c r="B113" s="12" t="s">
-        <v>238</v>
       </c>
       <c r="C113" s="13">
         <v>15840672</v>
@@ -7162,10 +6818,10 @@
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B114" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>240</v>
       </c>
       <c r="C114" s="7">
         <v>16307488</v>
@@ -7209,10 +6865,10 @@
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B115" s="12" t="s">
         <v>241</v>
-      </c>
-      <c r="B115" s="12" t="s">
-        <v>242</v>
       </c>
       <c r="C115" s="13">
         <v>17850212</v>
@@ -7256,10 +6912,10 @@
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B116" s="6" t="s">
         <v>243</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>244</v>
       </c>
       <c r="C116" s="7">
         <v>15603656</v>
@@ -7303,10 +6959,10 @@
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="B117" s="12" t="s">
         <v>245</v>
-      </c>
-      <c r="B117" s="12" t="s">
-        <v>246</v>
       </c>
       <c r="C117" s="13">
         <v>14831629</v>
@@ -7350,10 +7006,10 @@
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B118" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="C118" s="7">
         <v>15279246</v>
@@ -7397,10 +7053,10 @@
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="B119" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>250</v>
       </c>
       <c r="C119" s="13">
         <v>14274671</v>
@@ -7444,10 +7100,10 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A120" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B120" s="6" t="s">
         <v>251</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>252</v>
       </c>
       <c r="C120" s="7">
         <v>13160339</v>
@@ -7491,10 +7147,10 @@
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="B121" s="12" t="s">
         <v>253</v>
-      </c>
-      <c r="B121" s="12" t="s">
-        <v>254</v>
       </c>
       <c r="C121" s="13">
         <v>14743671</v>
@@ -7538,10 +7194,10 @@
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A122" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B122" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="C122" s="7">
         <v>12862738</v>
@@ -7585,10 +7241,10 @@
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B123" s="12" t="s">
         <v>257</v>
-      </c>
-      <c r="B123" s="12" t="s">
-        <v>258</v>
       </c>
       <c r="C123" s="13">
         <v>11834512</v>
@@ -7632,10 +7288,10 @@
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B124" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="C124" s="7">
         <v>16633462</v>
@@ -7679,10 +7335,10 @@
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="B125" s="12" t="s">
         <v>261</v>
-      </c>
-      <c r="B125" s="12" t="s">
-        <v>262</v>
       </c>
       <c r="C125" s="13">
         <v>15289055</v>
@@ -7726,10 +7382,10 @@
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A126" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B126" s="6" t="s">
         <v>263</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>264</v>
       </c>
       <c r="C126" s="7">
         <v>15697563</v>
@@ -7773,10 +7429,10 @@
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B127" s="12" t="s">
         <v>265</v>
-      </c>
-      <c r="B127" s="12" t="s">
-        <v>266</v>
       </c>
       <c r="C127" s="13">
         <v>17653727</v>
@@ -7820,10 +7476,10 @@
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B128" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="C128" s="7">
         <v>15402399</v>
@@ -7867,10 +7523,10 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>270</v>
       </c>
       <c r="C129" s="13">
         <v>15479542</v>
@@ -7914,10 +7570,10 @@
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B130" s="6" t="s">
         <v>271</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>272</v>
       </c>
       <c r="C130" s="7">
         <v>15698695</v>
@@ -7961,10 +7617,10 @@
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B131" s="12" t="s">
         <v>273</v>
-      </c>
-      <c r="B131" s="12" t="s">
-        <v>274</v>
       </c>
       <c r="C131" s="13">
         <v>13679232</v>
@@ -8008,10 +7664,10 @@
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B132" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>276</v>
       </c>
       <c r="C132" s="7">
         <v>12235765</v>
@@ -8055,10 +7711,10 @@
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="12" t="s">
+        <v>276</v>
+      </c>
+      <c r="B133" s="12" t="s">
         <v>277</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>278</v>
       </c>
       <c r="C133" s="13">
         <v>12343504</v>
@@ -8102,10 +7758,10 @@
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B134" s="6" t="s">
         <v>279</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>280</v>
       </c>
       <c r="C134" s="7">
         <v>13166975</v>
@@ -8149,10 +7805,10 @@
     </row>
     <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="B135" s="12" t="s">
         <v>281</v>
-      </c>
-      <c r="B135" s="12" t="s">
-        <v>282</v>
       </c>
       <c r="C135" s="13">
         <v>12150166</v>
@@ -8196,10 +7852,10 @@
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B136" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="C136" s="7">
         <v>16072634</v>
@@ -8243,10 +7899,10 @@
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="B137" s="12" t="s">
         <v>285</v>
-      </c>
-      <c r="B137" s="12" t="s">
-        <v>286</v>
       </c>
       <c r="C137" s="13">
         <v>13953353</v>
@@ -8290,10 +7946,10 @@
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B138" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>288</v>
       </c>
       <c r="C138" s="7">
         <v>13929361</v>
@@ -8337,10 +7993,10 @@
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="B139" s="12" t="s">
         <v>289</v>
-      </c>
-      <c r="B139" s="12" t="s">
-        <v>290</v>
       </c>
       <c r="C139" s="13">
         <v>16367901</v>
@@ -8384,10 +8040,10 @@
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B140" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="C140" s="7">
         <v>14732790</v>
@@ -8431,10 +8087,10 @@
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="B141" s="12" t="s">
         <v>293</v>
-      </c>
-      <c r="B141" s="12" t="s">
-        <v>294</v>
       </c>
       <c r="C141" s="13">
         <v>14617498</v>
@@ -8478,10 +8134,10 @@
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B142" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="C142" s="7">
         <v>14209057</v>
@@ -8525,10 +8181,10 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="12" t="s">
+        <v>296</v>
+      </c>
+      <c r="B143" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="B143" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="C143" s="13">
         <v>12075602</v>
@@ -8572,10 +8228,10 @@
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B144" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>300</v>
       </c>
       <c r="C144" s="7">
         <v>11736123</v>
@@ -8619,10 +8275,10 @@
     </row>
     <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A145" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="B145" s="12" t="s">
         <v>301</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>302</v>
       </c>
       <c r="C145" s="13">
         <v>12452969</v>
@@ -8666,10 +8322,10 @@
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B146" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>304</v>
       </c>
       <c r="C146" s="7">
         <v>13013283</v>
@@ -8713,10 +8369,10 @@
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="B147" s="12" t="s">
         <v>305</v>
-      </c>
-      <c r="B147" s="12" t="s">
-        <v>306</v>
       </c>
       <c r="C147" s="13">
         <v>12734764</v>
@@ -8760,10 +8416,10 @@
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B148" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="B148" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="C148" s="7">
         <v>14133277</v>
@@ -8807,10 +8463,10 @@
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A149" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="B149" s="12" t="s">
         <v>309</v>
-      </c>
-      <c r="B149" s="12" t="s">
-        <v>310</v>
       </c>
       <c r="C149" s="13">
         <v>13606150</v>
@@ -8854,10 +8510,10 @@
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B150" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="B150" s="6" t="s">
-        <v>312</v>
       </c>
       <c r="C150" s="7">
         <v>14490392</v>
@@ -8901,10 +8557,10 @@
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B151" s="12" t="s">
         <v>313</v>
-      </c>
-      <c r="B151" s="12" t="s">
-        <v>314</v>
       </c>
       <c r="C151" s="13">
         <v>15609777</v>
@@ -8948,10 +8604,10 @@
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B152" s="6" t="s">
         <v>315</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="C152" s="7">
         <v>13654356</v>
@@ -8995,10 +8651,10 @@
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B153" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="B153" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="C153" s="13">
         <v>13592465</v>
@@ -9042,10 +8698,10 @@
     </row>
     <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A154" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B154" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>320</v>
       </c>
       <c r="C154" s="7">
         <v>12667394</v>
@@ -9089,10 +8745,10 @@
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="B155" s="12" t="s">
         <v>321</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>322</v>
       </c>
       <c r="C155" s="13">
         <v>11801924</v>
@@ -9136,10 +8792,10 @@
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B156" s="6" t="s">
         <v>323</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>324</v>
       </c>
       <c r="C156" s="7">
         <v>10784138</v>
@@ -9183,10 +8839,10 @@
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="B157" s="12" t="s">
         <v>325</v>
-      </c>
-      <c r="B157" s="12" t="s">
-        <v>326</v>
       </c>
       <c r="C157" s="13">
         <v>11999016</v>
@@ -9230,10 +8886,10 @@
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B158" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="C158" s="7">
         <v>11630135</v>
@@ -9277,10 +8933,10 @@
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="12" t="s">
+        <v>328</v>
+      </c>
+      <c r="B159" s="12" t="s">
         <v>329</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>330</v>
       </c>
       <c r="C159" s="13">
         <v>11428603</v>
@@ -9324,10 +8980,10 @@
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B160" s="6" t="s">
         <v>331</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>332</v>
       </c>
       <c r="C160" s="7">
         <v>13550309</v>
@@ -9371,10 +9027,10 @@
     </row>
     <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A161" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="B161" s="12" t="s">
         <v>333</v>
-      </c>
-      <c r="B161" s="12" t="s">
-        <v>334</v>
       </c>
       <c r="C161" s="13">
         <v>13193841</v>
@@ -9418,10 +9074,10 @@
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B162" s="6" t="s">
         <v>335</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>336</v>
       </c>
       <c r="C162" s="7">
         <v>13952237</v>
@@ -9465,10 +9121,10 @@
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="B163" s="12" t="s">
         <v>337</v>
-      </c>
-      <c r="B163" s="12" t="s">
-        <v>338</v>
       </c>
       <c r="C163" s="13">
         <v>14868491</v>
@@ -9512,10 +9168,10 @@
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B164" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="C164" s="7">
         <v>12880486</v>
@@ -9559,10 +9215,10 @@
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="B165" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="B165" s="12" t="s">
-        <v>342</v>
       </c>
       <c r="C165" s="13">
         <v>11704373</v>
@@ -9606,10 +9262,10 @@
     </row>
     <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B166" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="C166" s="7">
         <v>12529357</v>
@@ -9653,10 +9309,10 @@
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="B167" s="12" t="s">
         <v>345</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>346</v>
       </c>
       <c r="C167" s="13">
         <v>11199180</v>
@@ -9696,939 +9352,6 @@
       </c>
       <c r="O167" s="14">
         <v>56.97</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>350</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>356</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>362</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>363</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>368</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>381</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>385</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>387</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>385</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>390</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>394</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>396</v>
-      </c>
-      <c r="C16" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>399</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="11" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="13">
-        <v>166</v>
-      </c>
-      <c r="C2" s="14">
-        <v>15085990.542168669</v>
-      </c>
-      <c r="D2" s="14">
-        <v>1766997.5799039849</v>
-      </c>
-      <c r="E2" s="14">
-        <v>10784138</v>
-      </c>
-      <c r="F2" s="14">
-        <v>13895916.5</v>
-      </c>
-      <c r="G2" s="14">
-        <v>15215430.5</v>
-      </c>
-      <c r="H2" s="14">
-        <v>16436340.75</v>
-      </c>
-      <c r="I2" s="14">
-        <v>18450246</v>
-      </c>
-      <c r="J2" s="13">
-        <v>0</v>
-      </c>
-      <c r="K2" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29">
-        <v>166</v>
-      </c>
-      <c r="C3" s="30">
-        <v>10756601.674698791</v>
-      </c>
-      <c r="D3" s="30">
-        <v>705456.62066127546</v>
-      </c>
-      <c r="E3" s="30">
-        <v>8884330</v>
-      </c>
-      <c r="F3" s="30">
-        <v>10191872.25</v>
-      </c>
-      <c r="G3" s="30">
-        <v>10751765.5</v>
-      </c>
-      <c r="H3" s="30">
-        <v>11234868.75</v>
-      </c>
-      <c r="I3" s="30">
-        <v>13078378</v>
-      </c>
-      <c r="J3" s="29">
-        <v>0</v>
-      </c>
-      <c r="K3" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="13">
-        <v>166</v>
-      </c>
-      <c r="C4" s="14">
-        <v>13954242.48192771</v>
-      </c>
-      <c r="D4" s="14">
-        <v>1657708.3048108821</v>
-      </c>
-      <c r="E4" s="14">
-        <v>10157478</v>
-      </c>
-      <c r="F4" s="14">
-        <v>12730448.5</v>
-      </c>
-      <c r="G4" s="14">
-        <v>14106640.5</v>
-      </c>
-      <c r="H4" s="14">
-        <v>15209857.75</v>
-      </c>
-      <c r="I4" s="14">
-        <v>17090082</v>
-      </c>
-      <c r="J4" s="13">
-        <v>0</v>
-      </c>
-      <c r="K4" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="29">
-        <v>166</v>
-      </c>
-      <c r="C5" s="30">
-        <v>400465.03012048191</v>
-      </c>
-      <c r="D5" s="30">
-        <v>140856.69979338549</v>
-      </c>
-      <c r="E5" s="30">
-        <v>165331</v>
-      </c>
-      <c r="F5" s="30">
-        <v>286685.75</v>
-      </c>
-      <c r="G5" s="30">
-        <v>395517.5</v>
-      </c>
-      <c r="H5" s="30">
-        <v>510586</v>
-      </c>
-      <c r="I5" s="30">
-        <v>756562</v>
-      </c>
-      <c r="J5" s="29">
-        <v>0</v>
-      </c>
-      <c r="K5" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="13">
-        <v>166</v>
-      </c>
-      <c r="C6" s="14">
-        <v>214.44015662650611</v>
-      </c>
-      <c r="D6" s="14">
-        <v>59.961992504137392</v>
-      </c>
-      <c r="E6" s="14">
-        <v>137.40799999999999</v>
-      </c>
-      <c r="F6" s="14">
-        <v>173.32499999999999</v>
-      </c>
-      <c r="G6" s="14">
-        <v>190.65</v>
-      </c>
-      <c r="H6" s="14">
-        <v>258.97975000000002</v>
-      </c>
-      <c r="I6" s="14">
-        <v>366.245</v>
-      </c>
-      <c r="J6" s="13">
-        <v>0</v>
-      </c>
-      <c r="K6" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="29">
-        <v>161</v>
-      </c>
-      <c r="C7" s="30">
-        <v>141.62077314426071</v>
-      </c>
-      <c r="D7" s="30">
-        <v>50.18547810706616</v>
-      </c>
-      <c r="E7" s="30">
-        <v>83.045230394509858</v>
-      </c>
-      <c r="F7" s="30">
-        <v>103.7097821771516</v>
-      </c>
-      <c r="G7" s="30">
-        <v>117.63113535469731</v>
-      </c>
-      <c r="H7" s="30">
-        <v>172.92872236422821</v>
-      </c>
-      <c r="I7" s="30">
-        <v>262.95586727553189</v>
-      </c>
-      <c r="J7" s="29">
-        <v>5</v>
-      </c>
-      <c r="K7" s="30">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="13">
-        <v>166</v>
-      </c>
-      <c r="C8" s="14">
-        <v>141.5615301204819</v>
-      </c>
-      <c r="D8" s="14">
-        <v>9.0981798037580841</v>
-      </c>
-      <c r="E8" s="14">
-        <v>126.3</v>
-      </c>
-      <c r="F8" s="14">
-        <v>135.4</v>
-      </c>
-      <c r="G8" s="14">
-        <v>140</v>
-      </c>
-      <c r="H8" s="14">
-        <v>149.14324999999999</v>
-      </c>
-      <c r="I8" s="14">
-        <v>158.84</v>
-      </c>
-      <c r="J8" s="13">
-        <v>0</v>
-      </c>
-      <c r="K8" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="29">
-        <v>166</v>
-      </c>
-      <c r="C9" s="30">
-        <v>291.07016867469878</v>
-      </c>
-      <c r="D9" s="30">
-        <v>22.920889011432489</v>
-      </c>
-      <c r="E9" s="30">
-        <v>240.7</v>
-      </c>
-      <c r="F9" s="30">
-        <v>277.60000000000002</v>
-      </c>
-      <c r="G9" s="30">
-        <v>291.8</v>
-      </c>
-      <c r="H9" s="30">
-        <v>308.92899999999997</v>
-      </c>
-      <c r="I9" s="30">
-        <v>331.54399999999998</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0</v>
-      </c>
-      <c r="K9" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="13">
-        <v>166</v>
-      </c>
-      <c r="C10" s="14">
-        <v>103.06858433734941</v>
-      </c>
-      <c r="D10" s="14">
-        <v>4.9764811370962123</v>
-      </c>
-      <c r="E10" s="14">
-        <v>87.384699999999995</v>
-      </c>
-      <c r="F10" s="14">
-        <v>100.015225</v>
-      </c>
-      <c r="G10" s="14">
-        <v>102.6297</v>
-      </c>
-      <c r="H10" s="14">
-        <v>106.5262</v>
-      </c>
-      <c r="I10" s="14">
-        <v>113.4663</v>
-      </c>
-      <c r="J10" s="13">
-        <v>0</v>
-      </c>
-      <c r="K10" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="29">
-        <v>166</v>
-      </c>
-      <c r="C11" s="30">
-        <v>15398.4</v>
-      </c>
-      <c r="D11" s="30">
-        <v>1739.2102577336821</v>
-      </c>
-      <c r="E11" s="30">
-        <v>12813.9</v>
-      </c>
-      <c r="F11" s="30">
-        <v>13882</v>
-      </c>
-      <c r="G11" s="30">
-        <v>15410.85</v>
-      </c>
-      <c r="H11" s="30">
-        <v>16921.075000000001</v>
-      </c>
-      <c r="I11" s="30">
-        <v>20520</v>
-      </c>
-      <c r="J11" s="29">
-        <v>0</v>
-      </c>
-      <c r="K11" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="13">
-        <v>166</v>
-      </c>
-      <c r="C12" s="14">
-        <v>87.168941686746976</v>
-      </c>
-      <c r="D12" s="14">
-        <v>14.768477110725771</v>
-      </c>
-      <c r="E12" s="14">
-        <v>53.797179999999997</v>
-      </c>
-      <c r="F12" s="14">
-        <v>76.983775000000009</v>
-      </c>
-      <c r="G12" s="14">
-        <v>88.012190000000004</v>
-      </c>
-      <c r="H12" s="14">
-        <v>100.6814</v>
-      </c>
-      <c r="I12" s="14">
-        <v>109.1007</v>
-      </c>
-      <c r="J12" s="13">
-        <v>0</v>
-      </c>
-      <c r="K12" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="29">
-        <v>166</v>
-      </c>
-      <c r="C13" s="30">
-        <v>146645.56626506019</v>
-      </c>
-      <c r="D13" s="30">
-        <v>7661.6476955504722</v>
-      </c>
-      <c r="E13" s="30">
-        <v>130426</v>
-      </c>
-      <c r="F13" s="30">
-        <v>140822.5</v>
-      </c>
-      <c r="G13" s="30">
-        <v>146845.5</v>
-      </c>
-      <c r="H13" s="30">
-        <v>152227.5</v>
-      </c>
-      <c r="I13" s="30">
-        <v>158548</v>
-      </c>
-      <c r="J13" s="29">
-        <v>0</v>
-      </c>
-      <c r="K13" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="13">
-        <v>166</v>
-      </c>
-      <c r="C14" s="14">
-        <v>35.560602409638548</v>
-      </c>
-      <c r="D14" s="14">
-        <v>3.1921355440947279</v>
-      </c>
-      <c r="E14" s="14">
-        <v>30.61</v>
-      </c>
-      <c r="F14" s="14">
-        <v>32.99</v>
-      </c>
-      <c r="G14" s="14">
-        <v>35.51</v>
-      </c>
-      <c r="H14" s="14">
-        <v>37.51</v>
-      </c>
-      <c r="I14" s="14">
-        <v>41.16</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0</v>
-      </c>
-      <c r="K14" s="14">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="31"/>
-    </row>
-    <row r="2" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-    </row>
-    <row r="3" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>416</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
-        <v>418</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-    </row>
-    <row r="8" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>420</v>
-      </c>
-      <c r="B8" s="31"/>
-    </row>
-    <row r="9" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>421</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>423</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>428</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-    </row>
-    <row r="15" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="31" t="s">
-        <v>430</v>
-      </c>
-      <c r="B15" s="31"/>
-    </row>
-    <row r="16" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>436</v>
       </c>
     </row>
   </sheetData>
